--- a/tests/fixtures/green_button/billed_period.xlsx
+++ b/tests/fixtures/green_button/billed_period.xlsx
@@ -230,10 +230,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="4">
-    <numFmt numFmtId="178" formatCode="yyyy/mm/dd\ hh:mm\ ddd"/>
+    <numFmt numFmtId="179" formatCode="yyyy/mm/dd\ hh:mm"/>
     <numFmt numFmtId="177" formatCode="#,##0.000"/>
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
-    <numFmt numFmtId="179" formatCode="yyyy/mm/dd\ hh:mm"/>
+    <numFmt numFmtId="178" formatCode="yyyy/mm/dd\ hh:mm\ ddd"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -793,10 +793,10 @@
         <v>46226</v>
       </c>
       <c r="B5" s="8">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D5" s="9">
-        <v>2575.319925</v>
+        <v>2471.039928</v>
       </c>
       <c r="F5" s="9">
         <v>120.959997</v>
@@ -870,7 +870,7 @@
         <v>744</v>
       </c>
       <c r="D6" s="9">
-        <v>77281.55776</v>
+        <v>77292.71776</v>
       </c>
       <c r="F6" s="9">
         <v>153.119996</v>
@@ -941,10 +941,10 @@
         <v>46165</v>
       </c>
       <c r="B7" s="8">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" s="9">
-        <v>2244.959931</v>
+        <v>2338.079928</v>
       </c>
       <c r="F7" s="9">
         <v>106.079997</v>
